--- a/influencer_forms/005_social_media_verification_request_form--influencer_forms.xlsx
+++ b/influencer_forms/005_social_media_verification_request_form--influencer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HH:MM</t>
+          <t>HH -MM</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HH:MM</t>
+          <t>HH -MM</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Select Multiple Social Media Platforms</t>
+          <t>Select Multiple 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -867,7 +867,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Additional Information</t>
+          <t>Note 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -885,12 +885,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>note_1</t>
+          <t>note_1_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note 1 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -908,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>note_2</t>
+          <t>note_2_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note 2 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -936,7 +936,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Select a Social Media Platform</t>
+          <t>Select One 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Select Multiple Social Media Platforms</t>
+          <t>Select Multiple 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -982,7 +982,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Date of Birth</t>
+          <t>Date 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Time of Verification</t>
+          <t>Time 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Additional Information</t>
+          <t>Note 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>note_2</t>
+          <t>note_2_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note 2 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>note_3</t>
+          <t>note_3_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note 3 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
